--- a/www/download/IND.gross_output.s.mv.rpO2.xlsx
+++ b/www/download/IND.gross_output.s.mv.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>349706.483</t>
+          <t>349706482539.463</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>366446.86</t>
+          <t>366446859982.686</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>289113.402</t>
+          <t>289113401978.484</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>285568.13</t>
+          <t>285568129633.589</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>472900.715</t>
+          <t>472900715075.232</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>601041.056</t>
+          <t>601041055516.363</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>592274.796</t>
+          <t>592274796257.506</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>616611.038</t>
+          <t>616611038329.906</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>717865.773</t>
+          <t>717865772679.263</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>943021.726</t>
+          <t>943021726224.442</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1110435.256</t>
+          <t>1110435256340.09</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1097810.093</t>
+          <t>1097810092728.64</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1063313.06</t>
+          <t>1063313059567.15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1019120.35</t>
+          <t>1019120350070.47</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>804032.086</t>
+          <t>804032085627.786</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>167082.74</t>
+          <t>167082740442.337</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>182995.206</t>
+          <t>182995206053.021</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>116392.789</t>
+          <t>116392789024.553</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>136155.214</t>
+          <t>136155214172.826</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>195207.8</t>
+          <t>195207800062.079</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>289598.273</t>
+          <t>289598272948.754</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>349472.541</t>
+          <t>349472540795.733</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>345718.54</t>
+          <t>345718539834.935</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>353819.13</t>
+          <t>353819130381.855</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>369698.007</t>
+          <t>369698006864.226</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>433410.226</t>
+          <t>433410226157.809</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>532570.257</t>
+          <t>532570257007.893</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>470682.302</t>
+          <t>470682302322.866</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>447340.627</t>
+          <t>447340627457.701</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>266988.56</t>
+          <t>266988560300.747</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>289659.592</t>
+          <t>289659592271.263</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>259257.189</t>
+          <t>259257188523.978</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>204985.461</t>
+          <t>204985460788.068</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>220130.545</t>
+          <t>220130545239.293</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>290646.147</t>
+          <t>290646147496.291</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>452918.594</t>
+          <t>452918593892.127</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>461788.592</t>
+          <t>461788592270.518</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>449888.317</t>
+          <t>449888317343.868</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>524409.573</t>
+          <t>524409572737.706</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>581650.389</t>
+          <t>581650389358.505</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>726273.369</t>
+          <t>726273368904.091</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>770104.671</t>
+          <t>770104670567.067</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>689300.462</t>
+          <t>689300461983.721</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>677656.968</t>
+          <t>677656968421.879</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>419177.938</t>
+          <t>419177938008.351</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>43476.993</t>
+          <t>43476993247.6867</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44827.46</t>
+          <t>44827459989.3273</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34449.335</t>
+          <t>34449334656.4828</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31309.331</t>
+          <t>31309331393.7428</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>33800.969</t>
+          <t>33800968881.2369</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>41183.189</t>
+          <t>41183188693.1819</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>53035.137</t>
+          <t>53035137409.2544</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>59019.198</t>
+          <t>59019197661.8142</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>73042.494</t>
+          <t>73042493536.9074</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>92893.429</t>
+          <t>92893428605.7119</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>104874.321</t>
+          <t>104874321023.843</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>133294.017</t>
+          <t>133294017047.266</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>133916.824</t>
+          <t>133916824223.377</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>133879.352</t>
+          <t>133879351815.532</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>92352.64</t>
+          <t>92352640033.4873</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1115508.531</t>
+          <t>1115508531061.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1122538.918</t>
+          <t>1122538917510.14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1046882.357</t>
+          <t>1046882357283.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1036504.081</t>
+          <t>1036504080572.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1118164.567</t>
+          <t>1118164566993.52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1554498.363</t>
+          <t>1554498363018.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1596324.643</t>
+          <t>1596324643370.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1487259.916</t>
+          <t>1487259915998.09</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1533606.775</t>
+          <t>1533606775064.34</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1815324.408</t>
+          <t>1815324408341.98</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1913741.951</t>
+          <t>1913741950851.86</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2016052.065</t>
+          <t>2016052064822.94</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2096142.195</t>
+          <t>2096142194728.72</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2329442.469</t>
+          <t>2329442468646.74</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1640779.761</t>
+          <t>1640779761210.09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>451961.958</t>
+          <t>451961957736.931</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>466823.553</t>
+          <t>466823553356.049</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>398025.495</t>
+          <t>398025494548.183</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>425478.434</t>
+          <t>425478434182.63</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>605851.159</t>
+          <t>605851158688.271</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1023903.025</t>
+          <t>1023903025453.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1150639.991</t>
+          <t>1150639991408.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>896976.353</t>
+          <t>896976352961.424</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>948536.135</t>
+          <t>948536134979.24</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1143638.309</t>
+          <t>1143638308529.76</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1383232.844</t>
+          <t>1383232843705.22</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1484310.413</t>
+          <t>1484310413313.19</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1244898.382</t>
+          <t>1244898382379.47</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1139068.906</t>
+          <t>1139068905557.6</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>768524.354</t>
+          <t>768524353609.725</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15049742.522</t>
+          <t>15049742521993</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15397255.163</t>
+          <t>15397255163154</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13922411.032</t>
+          <t>13922411032431.7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13120282.217</t>
+          <t>13120282216662.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12349985.849</t>
+          <t>12349985849413.6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14636549.579</t>
+          <t>14636549579192</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16598079.245</t>
+          <t>16598079244919.5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17997976.43</t>
+          <t>17997976430381.9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21682442.493</t>
+          <t>21682442493381.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25398142.776</t>
+          <t>25398142776003.9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>29363614.059</t>
+          <t>29363614058651.9</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>31634226.882</t>
+          <t>31634226882438.1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>32504957.244</t>
+          <t>32504957244492.5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>34339622.784</t>
+          <t>34339622784117.6</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>30828591.565</t>
+          <t>30828591565499.2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9414.379</t>
+          <t>9414379032.89725</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11460.942</t>
+          <t>11460942482.9468</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6730.714</t>
+          <t>6730713750.684</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7934.404</t>
+          <t>7934404479.07536</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13261.115</t>
+          <t>13261115308.4496</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17722.891</t>
+          <t>17722890826.3625</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22124.412</t>
+          <t>22124412257.9217</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24669.563</t>
+          <t>24669563318.3365</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29203.814</t>
+          <t>29203814015.9115</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26924.327</t>
+          <t>26924327429.3987</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18847.5</t>
+          <t>18847500237.3625</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19049.798</t>
+          <t>19049798404.8509</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>16619.786</t>
+          <t>16619786137.0186</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>18514.548</t>
+          <t>18514547794.1401</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>10515.735</t>
+          <t>10515734755.5875</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>80721.004</t>
+          <t>80721003662.2614</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>102087.694</t>
+          <t>102087693710.12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>66534.662</t>
+          <t>66534661793.4334</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>90847.911</t>
+          <t>90847911086.8819</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>120022.879</t>
+          <t>120022878559.052</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>171964.025</t>
+          <t>171964024881.976</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>227746.159</t>
+          <t>227746158743.77</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>249805.531</t>
+          <t>249805530979.579</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>271946.204</t>
+          <t>271946204408.886</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>271112.059</t>
+          <t>271112059440.791</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>324223.889</t>
+          <t>324223888676.563</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>353490.932</t>
+          <t>353490932309.21</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>304521.347</t>
+          <t>304521347431.364</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>290297.675</t>
+          <t>290297674994.695</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>149204.856</t>
+          <t>149204855987.7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1646431.526</t>
+          <t>1646431526274.72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1501324.474</t>
+          <t>1501324473772.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1178472.548</t>
+          <t>1178472548161.25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1450318.18</t>
+          <t>1450318180175.51</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1948569.057</t>
+          <t>1948569057371.35</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2843400.665</t>
+          <t>2843400664763.92</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3152051.631</t>
+          <t>3152051630830.48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3017890.386</t>
+          <t>3017890386073.3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3289927.516</t>
+          <t>3289927516285.2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3422334.354</t>
+          <t>3422334353579.51</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3739435.728</t>
+          <t>3739435728275.77</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4161687.273</t>
+          <t>4161687272962.46</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3607949.234</t>
+          <t>3607949234150.11</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3152738.679</t>
+          <t>3152738679432.55</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1731181.872</t>
+          <t>1731181872037.04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>133518.939</t>
+          <t>133518939490.487</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>137811.584</t>
+          <t>137811584300.214</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>110323.481</t>
+          <t>110323480715.101</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>130934.732</t>
+          <t>130934732477.287</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>137031.409</t>
+          <t>137031408906.718</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>190472.091</t>
+          <t>190472091107.522</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>216706.359</t>
+          <t>216706358799.581</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>200976.795</t>
+          <t>200976794623.97</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>236579.381</t>
+          <t>236579381026.656</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>259912.831</t>
+          <t>259912830756.824</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>306187.915</t>
+          <t>306187914644.792</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>305797.134</t>
+          <t>305797133958.861</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>272929.858</t>
+          <t>272929858314.832</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>258316.773</t>
+          <t>258316773472.211</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>155588.553</t>
+          <t>155588552517.566</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>529460.446</t>
+          <t>529460446179.946</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>539991.756</t>
+          <t>539991755978.886</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>460257.086</t>
+          <t>460257085788.373</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>490631.442</t>
+          <t>490631441957.657</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>723431.228</t>
+          <t>723431228392.739</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1302565.812</t>
+          <t>1302565812348.08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1390708.621</t>
+          <t>1390708621430.1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1360847.319</t>
+          <t>1360847319469.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1552220.585</t>
+          <t>1552220585292.73</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1818724.883</t>
+          <t>1818724882601.42</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2342620.796</t>
+          <t>2342620795759.27</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2646366.143</t>
+          <t>2646366142542.42</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2141118.538</t>
+          <t>2141118537551.22</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2126186.582</t>
+          <t>2126186581650.55</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1255203.785</t>
+          <t>1255203785054.51</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14906.135</t>
+          <t>14906134639.704</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14333.31</t>
+          <t>14333310051.216</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20453.675</t>
+          <t>20453674981.9188</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23129.147</t>
+          <t>23129147061.9229</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9978.931</t>
+          <t>9978931392.30158</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>37963.519</t>
+          <t>37963519409.5201</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>47739.11</t>
+          <t>47739109887.5012</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>47389.368</t>
+          <t>47389368221.2031</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>57686.991</t>
+          <t>57686991448.5568</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>37815.585</t>
+          <t>37815585086.9987</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>32089.429</t>
+          <t>32089428984.7823</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>33444.526</t>
+          <t>33444525886.6421</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>32545.555</t>
+          <t>32545554602.8036</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>31148.387</t>
+          <t>31148386818.062</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>15212.725</t>
+          <t>15212725214.4573</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>121396.816</t>
+          <t>121396815797.037</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>110415.001</t>
+          <t>110415000916.338</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79834.789</t>
+          <t>79834789452.1241</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93438.216</t>
+          <t>93438216321.9926</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>128833.042</t>
+          <t>128833042285.39</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>195379.772</t>
+          <t>195379772331.526</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>202007.705</t>
+          <t>202007705106.002</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>189191.648</t>
+          <t>189191648442.442</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>223493.824</t>
+          <t>223493824381.32</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>242556.437</t>
+          <t>242556436803.001</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>255652.722</t>
+          <t>255652721646.893</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>300833.73</t>
+          <t>300833730493.621</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>256096.404</t>
+          <t>256096403538.364</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>230933.693</t>
+          <t>230933692724.997</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>114111.915</t>
+          <t>114111914655.407</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1108669.255</t>
+          <t>1108669254622.79</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1026098.075</t>
+          <t>1026098075450.18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>772716.02</t>
+          <t>772716019649.319</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>919634.232</t>
+          <t>919634232113.86</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1309701.627</t>
+          <t>1309701626700.51</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2060844.126</t>
+          <t>2060844126039.34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2072288.026</t>
+          <t>2072288025703.99</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1993276.087</t>
+          <t>1993276086865.54</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2248458.074</t>
+          <t>2248458073655.27</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2387164.033</t>
+          <t>2387164032701.49</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3042267.001</t>
+          <t>3042267000612.63</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3223980.461</t>
+          <t>3223980460611.35</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2601634.206</t>
+          <t>2601634205730</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2521381.257</t>
+          <t>2521381256853.01</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1433497.069</t>
+          <t>1433497069346.34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1149802.464</t>
+          <t>1149802463592.84</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1134403.981</t>
+          <t>1134403981398.14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>896600.322</t>
+          <t>896600322381.356</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>962010.823</t>
+          <t>962010823047.645</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1216462.832</t>
+          <t>1216462832113.07</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1658734.947</t>
+          <t>1658734946704.69</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1586520.848</t>
+          <t>1586520847797.32</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1475541.633</t>
+          <t>1475541633324.89</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1639828.21</t>
+          <t>1639828209694.31</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1840553.035</t>
+          <t>1840553035294.72</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2295473.536</t>
+          <t>2295473536375.04</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2459565.363</t>
+          <t>2459565363127.07</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2126569.025</t>
+          <t>2126569024924.67</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1738748.292</t>
+          <t>1738748292328.36</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1066053.827</t>
+          <t>1066053827114.38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>98837.369</t>
+          <t>98837368503.9722</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>116582.125</t>
+          <t>116582125299.443</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>97245.909</t>
+          <t>97245909298.6779</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>101808.108</t>
+          <t>101808107745.274</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>125517.146</t>
+          <t>125517145932.276</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>277534.263</t>
+          <t>277534262554.749</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>256077.586</t>
+          <t>256077586466.54</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>227963.234</t>
+          <t>227963233717.323</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>265471.633</t>
+          <t>265471633172.916</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>296648.207</t>
+          <t>296648206772.751</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>371796.882</t>
+          <t>371796881895.693</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>513360.222</t>
+          <t>513360221846.308</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>411795.011</t>
+          <t>411795011141.878</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>418043.129</t>
+          <t>418043128851.193</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>270838.733</t>
+          <t>270838732542.706</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>73468.749</t>
+          <t>73468749059.1306</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>68667.377</t>
+          <t>68667377142.9141</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>66149.49</t>
+          <t>66149490454.9924</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>81904.518</t>
+          <t>81904517995.3992</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>104873.609</t>
+          <t>104873609467.506</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>152415.74</t>
+          <t>152415739854.594</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>183843.17</t>
+          <t>183843170321.15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>203690.755</t>
+          <t>203690754957.113</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>214441.053</t>
+          <t>214441052973.282</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>188617.943</t>
+          <t>188617942926.682</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>209643.913</t>
+          <t>209643913445.143</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>225949.939</t>
+          <t>225949939196.953</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>206998.216</t>
+          <t>206998215926.313</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>167643.849</t>
+          <t>167643848984.465</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>92730.47</t>
+          <t>92730469848.4201</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>880105.528</t>
+          <t>880105527984.871</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1016415.14</t>
+          <t>1016415140354.31</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>985801.467</t>
+          <t>985801466609.601</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>837493.944</t>
+          <t>837493943814.162</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>893379.794</t>
+          <t>893379793836.382</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1072898.95</t>
+          <t>1072898949916.64</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1071285.454</t>
+          <t>1071285453808.11</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1202470.853</t>
+          <t>1202470852979.78</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1245973.651</t>
+          <t>1245973650860.71</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1359489.917</t>
+          <t>1359489917159.54</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1339454.653</t>
+          <t>1339454652614.13</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1372010.407</t>
+          <t>1372010407132.8</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1261658.46</t>
+          <t>1261658459893.21</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1257221.164</t>
+          <t>1257221164084.1</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>992090.767</t>
+          <t>992090767462.819</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5115276.317</t>
+          <t>5115276317455.61</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4594938.404</t>
+          <t>4594938404009.08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4392229.585</t>
+          <t>4392229585449.04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3922885.119</t>
+          <t>3922885118584.56</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4260420.548</t>
+          <t>4260420548186.94</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6193010.457</t>
+          <t>6193010457287.93</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7279595.841</t>
+          <t>7279595841292.58</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8130357.156</t>
+          <t>8130357156185.87</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>9223151.019</t>
+          <t>9223151018768.41</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>10709157.456</t>
+          <t>10709157455643.6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11776661.477</t>
+          <t>11776661477191.7</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>12149708.827</t>
+          <t>12149708827041.3</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>12076457.399</t>
+          <t>12076457398814.2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11743997.081</t>
+          <t>11743997081190.7</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11169342.69</t>
+          <t>11169342689628.3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>132754.188</t>
+          <t>132754187903.251</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>130461.252</t>
+          <t>130461252054.355</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>110825.113</t>
+          <t>110825113121.045</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>116382.819</t>
+          <t>116382819439.682</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>168547.797</t>
+          <t>168547796543.842</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>225280.343</t>
+          <t>225280342678.173</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>207647.311</t>
+          <t>207647311040.395</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>176454.525</t>
+          <t>176454525241.584</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>208013.063</t>
+          <t>208013062505.808</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>227284.011</t>
+          <t>227284011065.581</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>251440.295</t>
+          <t>251440295400.243</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>256258.412</t>
+          <t>256258411572.954</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>211107.528</t>
+          <t>211107527516.8</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>205370.323</t>
+          <t>205370322997.503</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>155876.319</t>
+          <t>155876319489.624</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1203586.829</t>
+          <t>1203586829408.78</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1272542.239</t>
+          <t>1272542239005.07</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1058173.866</t>
+          <t>1058173865545.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1127964.596</t>
+          <t>1127964595901.74</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1480810.368</t>
+          <t>1480810368435.26</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2479664.265</t>
+          <t>2479664265375.98</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2571016.494</t>
+          <t>2571016493748.34</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2533323.257</t>
+          <t>2533323257253.54</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2877834.373</t>
+          <t>2877834373257.71</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3044988.624</t>
+          <t>3044988623856.63</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3739166.009</t>
+          <t>3739166008748.19</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4513422.683</t>
+          <t>4513422683283.15</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>3672710.89</t>
+          <t>3672710889655.89</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3416275.534</t>
+          <t>3416275533575.62</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1950346.899</t>
+          <t>1950346898584.83</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4014101.202</t>
+          <t>4014101202033</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3594049.096</t>
+          <t>3594049096480.15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3508005.818</t>
+          <t>3508005818248.37</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3200522.251</t>
+          <t>3200522250853.03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4172245.62</t>
+          <t>4172245620091.94</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7005847.197</t>
+          <t>7005847196814.77</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6925520.162</t>
+          <t>6925520161576.08</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6323874.503</t>
+          <t>6323874502979.47</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7116358.426</t>
+          <t>7116358426057.76</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7935889.687</t>
+          <t>7935889687030.52</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9966042.936</t>
+          <t>9966042935597.29</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>10694274.713</t>
+          <t>10694274713109.1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>9040666.347</t>
+          <t>9040666347255.62</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10393144.603</t>
+          <t>10393144603235.7</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5749835.763</t>
+          <t>5749835762717.45</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1510915.983</t>
+          <t>1510915982982.6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1659011.257</t>
+          <t>1659011256842.75</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1685044.775</t>
+          <t>1685044775131.68</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1456008.99</t>
+          <t>1456008989612.39</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1940867.902</t>
+          <t>1940867901915.93</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3227187.697</t>
+          <t>3227187697445.54</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3183685.73</t>
+          <t>3183685730017.6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3137087.693</t>
+          <t>3137087692893.54</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3655764.882</t>
+          <t>3655764882141.91</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4153439.027</t>
+          <t>4153439027248.47</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5241839.614</t>
+          <t>5241839613529.24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5955091.001</t>
+          <t>5955091001414.6</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5148246.217</t>
+          <t>5148246217390.26</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5622680.239</t>
+          <t>5622680238626.08</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3645323.294</t>
+          <t>3645323294473.76</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>26166.422</t>
+          <t>26166422457.2204</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>31329.863</t>
+          <t>31329862729.2881</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19614.187</t>
+          <t>19614186589.8713</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>18769.878</t>
+          <t>18769877961.9444</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20496.12</t>
+          <t>20496119749.4032</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23843.334</t>
+          <t>23843334024.1073</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28667.069</t>
+          <t>28667068623.2977</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>28421.23</t>
+          <t>28421229980.1775</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>35679.468</t>
+          <t>35679468091.3399</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>36920.983</t>
+          <t>36920982818.9217</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>49071.967</t>
+          <t>49071967164.126</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>53124.153</t>
+          <t>53124152540.564</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>60737.412</t>
+          <t>60737411968.6832</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>54533.859</t>
+          <t>54533858543.9739</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>27261.849</t>
+          <t>27261848898.0462</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13052.485</t>
+          <t>13052484970.0113</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9603.687</t>
+          <t>9603686599.42789</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8513.633</t>
+          <t>8513632587.59741</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>9771.913</t>
+          <t>9771913156.44311</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11455.324</t>
+          <t>11455323657.1459</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>15078.685</t>
+          <t>15078684526.9368</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14565.376</t>
+          <t>14565375858.9595</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>12802.281</t>
+          <t>12802281378.2777</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16693.42</t>
+          <t>16693419876.996</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>18564.089</t>
+          <t>18564088828.0943</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>21483.837</t>
+          <t>21483836568.6976</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>22196.03</t>
+          <t>22196029769.0345</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>19545.066</t>
+          <t>19545065716.3058</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>17249.21</t>
+          <t>17249209592.6013</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>16872.426</t>
+          <t>16872425975.8847</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9308.202</t>
+          <t>9308202489.26403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10058.995</t>
+          <t>10058995249.4649</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7829.916</t>
+          <t>7829916198.29902</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10767.456</t>
+          <t>10767455962.2983</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13550.167</t>
+          <t>13550167332.8718</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>16460.531</t>
+          <t>16460530746.7849</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>21039.624</t>
+          <t>21039623501.9258</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>21939.465</t>
+          <t>21939465345.2813</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>28558.6</t>
+          <t>28558600377.7231</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>44261.424</t>
+          <t>44261423775.2419</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>250086.58</t>
+          <t>250086580219.43</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>74900.417</t>
+          <t>74900416811.177</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>43587.719</t>
+          <t>43587718962.2572</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>38119.071</t>
+          <t>38119071178.9836</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>23127.187</t>
+          <t>23127186899.8583</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>431363.961</t>
+          <t>431363961351.208</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>461352.394</t>
+          <t>461352393733.989</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>436889.619</t>
+          <t>436889619127.555</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>536572.204</t>
+          <t>536572204169.286</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>692855.111</t>
+          <t>692855110752.393</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>969214.278</t>
+          <t>969214278387.051</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1140532.852</t>
+          <t>1140532852254.13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1133177.95</t>
+          <t>1133177949539.55</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1098543.317</t>
+          <t>1098543317141.51</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1190981.18</t>
+          <t>1190981179588.9</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1317150.544</t>
+          <t>1317150543837.36</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1337523.23</t>
+          <t>1337523230403.25</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1121927.79</t>
+          <t>1121927790180.37</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1077966.033</t>
+          <t>1077966032623.52</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>752281.407</t>
+          <t>752281407198.748</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>11167.724</t>
+          <t>11167724456.4558</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>11163.941</t>
+          <t>11163940638.9487</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6826.086</t>
+          <t>6826085919.28434</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9476.46</t>
+          <t>9476459582.43561</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15474.865</t>
+          <t>15474864678.9609</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>27289.162</t>
+          <t>27289162361.1751</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17055.773</t>
+          <t>17055773362.3811</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16316.234</t>
+          <t>16316234410.3498</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17971.114</t>
+          <t>17971113825.7043</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>16594.031</t>
+          <t>16594031284.3506</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19964.65</t>
+          <t>19964650316.2471</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>20938.265</t>
+          <t>20938264650.8959</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>16887.53</t>
+          <t>16887529808.0695</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>16951.808</t>
+          <t>16951807619.2244</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11035.516</t>
+          <t>11035515554.8305</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>542003.826</t>
+          <t>542003825813.047</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>524429.747</t>
+          <t>524429746938.289</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>398442.828</t>
+          <t>398442827815.739</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>474391.48</t>
+          <t>474391479673.129</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>613278.849</t>
+          <t>613278849228.537</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>829937.482</t>
+          <t>829937482214.036</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>802181.788</t>
+          <t>802181787886.876</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>700823.823</t>
+          <t>700823822530.624</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>792091.842</t>
+          <t>792091841594.007</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>875883.377</t>
+          <t>875883377067.546</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1170463.843</t>
+          <t>1170463843459.42</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1284494.343</t>
+          <t>1284494342642.8</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1063198.007</t>
+          <t>1063198006635.24</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1139665.3</t>
+          <t>1139665299931.46</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>702970.708</t>
+          <t>702970707951.971</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>184364.716</t>
+          <t>184364716381.107</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>192186.32</t>
+          <t>192186319997.857</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>151019.537</t>
+          <t>151019536917.238</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>182148.838</t>
+          <t>182148838244.531</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>215967.787</t>
+          <t>215967786762.224</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>302206.996</t>
+          <t>302206995817.256</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>312844.983</t>
+          <t>312844982687.946</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>335621.625</t>
+          <t>335621625466.339</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>367191.757</t>
+          <t>367191756715.836</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>410562.864</t>
+          <t>410562863735.729</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>505772.829</t>
+          <t>505772829303.617</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>557055.227</t>
+          <t>557055227354.662</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>552063.426</t>
+          <t>552063425918.097</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>489033.8</t>
+          <t>489033799565.316</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>294512.88</t>
+          <t>294512880481.212</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>121599.106</t>
+          <t>121599105833.026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>118327.817</t>
+          <t>118327816947.965</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>100226.496</t>
+          <t>100226496194.878</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>105489.148</t>
+          <t>105489147655.796</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>143653.951</t>
+          <t>143653950598.456</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>254668.478</t>
+          <t>254668478107.288</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>254369.838</t>
+          <t>254369837570.426</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>236076.067</t>
+          <t>236076066778.764</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>262965.491</t>
+          <t>262965490509.593</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>317122.14</t>
+          <t>317122139970.941</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>436098.42</t>
+          <t>436098420450.069</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>451540.337</t>
+          <t>451540336721.2</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>401988.821</t>
+          <t>401988821486.509</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>437087.929</t>
+          <t>437087929147.665</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>231816.798</t>
+          <t>231816798273.797</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>213174.491</t>
+          <t>213174490695.483</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>199442.521</t>
+          <t>199442521320.48</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>173140.078</t>
+          <t>173140078490.546</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>160940.837</t>
+          <t>160940836629.397</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>169737.21</t>
+          <t>169737209909.338</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>204882.725</t>
+          <t>204882724766.077</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>259221.186</t>
+          <t>259221185789.684</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>266506.905</t>
+          <t>266506905414.757</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>270002.184</t>
+          <t>270002184207.011</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>307461.57</t>
+          <t>307461570156.442</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>341796.732</t>
+          <t>341796731782.486</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>401550.324</t>
+          <t>401550323933.926</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>246656.034</t>
+          <t>246656033904.122</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>284057.104</t>
+          <t>284057104110.926</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>184488.233</t>
+          <t>184488232737.003</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1090310.772</t>
+          <t>1090310771583.45</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1018086.262</t>
+          <t>1018086262439.69</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>788662.878</t>
+          <t>788662877839.286</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>775146.923</t>
+          <t>775146922750.513</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>660565.048</t>
+          <t>660565047813.872</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>916468.831</t>
+          <t>916468831101.121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>953118.078</t>
+          <t>953118078482.59</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>884193.023</t>
+          <t>884193023499.582</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>984916.502</t>
+          <t>984916501573.24</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1078250.461</t>
+          <t>1078250461425.54</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1255010.74</t>
+          <t>1255010740245.31</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1200067.373</t>
+          <t>1200067372901.16</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1166022.745</t>
+          <t>1166022744817.84</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1171783.784</t>
+          <t>1171783784300.07</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>823357.152</t>
+          <t>823357151763.13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>33521.379</t>
+          <t>33521378824.6195</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>35681.983</t>
+          <t>35681982858.3389</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>28310.691</t>
+          <t>28310691360.709</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>34527.495</t>
+          <t>34527495287.8418</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>38963.749</t>
+          <t>38963749482.8929</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>51725.162</t>
+          <t>51725161695.2607</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>64260.422</t>
+          <t>64260421846.759</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>62719.164</t>
+          <t>62719164121.3755</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>80055.914</t>
+          <t>80055913690.0632</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>120484.502</t>
+          <t>120484502112.186</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>151503.621</t>
+          <t>151503621156.291</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>167369.864</t>
+          <t>167369864421.608</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>166016.682</t>
+          <t>166016682313.262</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>144381.406</t>
+          <t>144381406108.957</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>115258.553</t>
+          <t>115258552697.461</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>30019.704</t>
+          <t>30019703540.3617</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>29962.215</t>
+          <t>29962214548.2136</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22568.605</t>
+          <t>22568604983.0216</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26124.091</t>
+          <t>26124090700.1467</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>34307.623</t>
+          <t>34307623496.7103</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>46330.936</t>
+          <t>46330936186.2296</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>49676.734</t>
+          <t>49676734359.4243</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>51725.986</t>
+          <t>51725985705.1615</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>61804.683</t>
+          <t>61804683355.3728</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>64228.394</t>
+          <t>64228393829.3915</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>75466.493</t>
+          <t>75466492934.3539</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>82126.426</t>
+          <t>82126426051.0199</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>76350.288</t>
+          <t>76350287858.5296</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>90015.535</t>
+          <t>90015534571.5697</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>50990.101</t>
+          <t>50990101314.1807</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>223682.388</t>
+          <t>223682387637.012</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>213272.573</t>
+          <t>213272572872.82</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>165700.044</t>
+          <t>165700044267.499</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>191176.711</t>
+          <t>191176710816.963</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>259098.93</t>
+          <t>259098929681.642</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>407255.507</t>
+          <t>407255506510.521</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>397716.528</t>
+          <t>397716527558.294</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>346165.088</t>
+          <t>346165087690.438</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>403440.519</t>
+          <t>403440518619.855</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>403439.408</t>
+          <t>403439407816.781</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>454259.008</t>
+          <t>454259008322.072</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>483565.347</t>
+          <t>483565346946.537</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>412661.249</t>
+          <t>412661248543.3</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>342356.698</t>
+          <t>342356697769.008</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>200353.917</t>
+          <t>200353917452.712</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>433799.389</t>
+          <t>433799389259.801</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>463723.161</t>
+          <t>463723160628.158</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>541565.585</t>
+          <t>541565585284.399</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>558249.606</t>
+          <t>558249606466.194</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>616200.797</t>
+          <t>616200797097.703</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1266998.533</t>
+          <t>1266998532889.34</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1251834.154</t>
+          <t>1251834153970.24</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1843932.085</t>
+          <t>1843932085303.2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2159172.09</t>
+          <t>2159172089958.23</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2258443.438</t>
+          <t>2258443437805.64</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2689046.614</t>
+          <t>2689046614450.49</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2882614.171</t>
+          <t>2882614170688.34</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2482085.458</t>
+          <t>2482085457670.68</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1876992.636</t>
+          <t>1876992636352.48</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1573730.919</t>
+          <t>1573730919249.83</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>858003.594</t>
+          <t>858003593634.243</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>805607.806</t>
+          <t>805607806459.304</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>729496.572</t>
+          <t>729496572038.025</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>802681.842</t>
+          <t>802681842052.994</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1073502.422</t>
+          <t>1073502421990.41</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1821161.561</t>
+          <t>1821161561458.36</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1711815.298</t>
+          <t>1711815298029.21</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1938413.456</t>
+          <t>1938413456359.72</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2116320.307</t>
+          <t>2116320307000.78</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2397626.983</t>
+          <t>2397626982932.91</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2633884.047</t>
+          <t>2633884047023.11</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2801646.653</t>
+          <t>2801646653175.31</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2359821.097</t>
+          <t>2359821096917.41</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2315569.427</t>
+          <t>2315569426525.06</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1318697.381</t>
+          <t>1318697380754.27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5372842.254</t>
+          <t>5372842253629.57</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5329512.587</t>
+          <t>5329512586935.29</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4896521.437</t>
+          <t>4896521437433.17</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4896550.65</t>
+          <t>4896550650412.79</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6772038.626</t>
+          <t>6772038626097.97</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11202791.477</t>
+          <t>11202791476696.7</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10572052.42</t>
+          <t>10572052420055.6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>9612340.717</t>
+          <t>9612340716711.2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>10232900.85</t>
+          <t>10232900849881.5</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>11458638.915</t>
+          <t>11458638915410</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>14439160.664</t>
+          <t>14439160663707.7</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>14631217.359</t>
+          <t>14631217359383.1</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>12153424.313</t>
+          <t>12153424313153.4</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>12468601.796</t>
+          <t>12468601795951.8</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>6412535.804</t>
+          <t>6412535803805.99</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>86740329.672</t>
+          <t>86740329672008.9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>85590915.961</t>
+          <t>85590915961318.4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>92001522.72</t>
+          <t>92001522720327</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>93848686.521</t>
+          <t>93848686521454.1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>103276525.208</t>
+          <t>103276525208076</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>130259226.62</t>
+          <t>130259226620294</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>135071065.661</t>
+          <t>135071065661346</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>131253887.748</t>
+          <t>131253887748282</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>142667566.186</t>
+          <t>142667566186379</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>143293364.703</t>
+          <t>143293364703016</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>158696553.005</t>
+          <t>158696553004531</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>160544122.377</t>
+          <t>160544122377194</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>141110805.407</t>
+          <t>141110805407410</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>140162270.41</t>
+          <t>140162270410476</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>120354501.377</t>
+          <t>120354501376679</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>131625216.032</t>
+          <t>131625216032481</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>129915395.89</t>
+          <t>129915395890034</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>131984510.105</t>
+          <t>131984510104617</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>132910749.438</t>
+          <t>132910749437501</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>148448183.898</t>
+          <t>148448183898456</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>196328119.137</t>
+          <t>196328119136838</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>204320197.348</t>
+          <t>204320197348442</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>201093322.949</t>
+          <t>201093322948556</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>221785949.316</t>
+          <t>221785949315506</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>232859809.921</t>
+          <t>232859809920901</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>264795199.915</t>
+          <t>264795199914741</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>273848711.858</t>
+          <t>273848711858407</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>245046613.533</t>
+          <t>245046613532936</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>245805409.068</t>
+          <t>245805409068070</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>197871194.383</t>
+          <t>197871194383408</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
